--- a/artfynd/A 26900-2025 artfynd.xlsx
+++ b/artfynd/A 26900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814956</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814948</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814967</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814947</v>
       </c>
       <c r="B5" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814949</v>
       </c>
       <c r="B6" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814980</v>
       </c>
       <c r="B7" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814973</v>
       </c>
       <c r="B8" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814950</v>
+        <v>126814955</v>
       </c>
       <c r="B9" t="n">
-        <v>80112</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677528</v>
+        <v>677526</v>
       </c>
       <c r="R9" t="n">
-        <v>7109526</v>
+        <v>7109531</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814955</v>
+        <v>126814950</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677526</v>
+        <v>677528</v>
       </c>
       <c r="R10" t="n">
-        <v>7109531</v>
+        <v>7109526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>126837620</v>
       </c>
       <c r="B11" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26900-2025 artfynd.xlsx
+++ b/artfynd/A 26900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814956</v>
       </c>
       <c r="B2" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814948</v>
       </c>
       <c r="B3" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814967</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814947</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814949</v>
       </c>
       <c r="B6" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814980</v>
       </c>
       <c r="B7" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814973</v>
       </c>
       <c r="B8" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126814955</v>
       </c>
       <c r="B9" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126814950</v>
       </c>
       <c r="B10" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126837620</v>
       </c>
       <c r="B11" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26900-2025 artfynd.xlsx
+++ b/artfynd/A 26900-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>126814973</v>
       </c>
       <c r="B8" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26900-2025 artfynd.xlsx
+++ b/artfynd/A 26900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814956</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814948</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814967</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814947</v>
       </c>
       <c r="B5" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814949</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814980</v>
       </c>
       <c r="B7" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814973</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126814955</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126814950</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126837620</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26900-2025 artfynd.xlsx
+++ b/artfynd/A 26900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814956</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814948</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>80143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814967</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814947</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814949</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>80143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814980</v>
       </c>
       <c r="B7" t="n">
-        <v>78424</v>
+        <v>78417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814973</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126814955</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126814950</v>
       </c>
       <c r="B10" t="n">
-        <v>80150</v>
+        <v>80143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126837620</v>
       </c>
       <c r="B11" t="n">
-        <v>80150</v>
+        <v>80143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26900-2025 artfynd.xlsx
+++ b/artfynd/A 26900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814956</v>
       </c>
       <c r="B2" t="n">
-        <v>80114</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814948</v>
       </c>
       <c r="B3" t="n">
-        <v>80143</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814967</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814947</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814949</v>
       </c>
       <c r="B6" t="n">
-        <v>80143</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814980</v>
       </c>
       <c r="B7" t="n">
-        <v>78417</v>
+        <v>78424</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814973</v>
       </c>
       <c r="B8" t="n">
-        <v>98353</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126814955</v>
       </c>
       <c r="B9" t="n">
-        <v>80114</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126814950</v>
       </c>
       <c r="B10" t="n">
-        <v>80143</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126837620</v>
       </c>
       <c r="B11" t="n">
-        <v>80143</v>
+        <v>80150</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
